--- a/config.xlsx
+++ b/config.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ec0213fddacd4dc585ef41093f5f235ed956adfb24eb449bb6d18115f64b0ec3</t>
+          <t>1a900760178748a1b88643e0fc78daa1f93109ee420c4b24b3e1d2d5010d42e2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D:\xwechat_files\q453497_ec01\db_storage</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -564,12 +564,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-11-16 09:46:59</t>
+          <t>2025-11-26 15:59:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>最后更新时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>llm_api_base</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://api.deepseek.com/v1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>API地址(OpenAI兼容格式,如https://api.deepseek.com/v1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>llm_api_key</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sk-53e2bce1b242455c9991cb9199510589</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>API密钥</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>llm_model</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>模型名称(如deepseek-chat, gpt-4o等)</t>
         </is>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>C:\Users\45349\xwechat_files\q453497_ec01\db_storage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-11-26 15:59:06</t>
+          <t>2025-11-27 11:17:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">

--- a/config.xlsx
+++ b/config.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>张雨蒙</t>
+          <t>张雨蒙，🌈南宁年度策略会客户汇总群</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-11-27 11:17:34</t>
+          <t>2025-11-27 22:00:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">

--- a/config.xlsx
+++ b/config.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>张雨蒙，🌈南宁年度策略会客户汇总群</t>
+          <t>🌈南宁年度策略会客户汇总群</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-11-27 22:00:14</t>
+          <t>2025-12-09 09:25:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
